--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="322">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -505,6 +505,9 @@
     <t>The current state of the Invoice.</t>
   </si>
   <si>
+    <t>issued</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -512,6 +515,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/invoice-status|4.0.1</t>
+  </si>
+  <si>
+    <t>1843: fixed value = #issued</t>
   </si>
   <si>
     <t>Varies by domain</t>
@@ -987,7 +993,7 @@
     <t>Derived Profiles may chose to add invariants requiring this field to be populated if either priceOverride or factorOverride have been filled.</t>
   </si>
   <si>
-    <t>1842: source value from AR CCPC STATEMENTS - SPECIAL NOTICES (349.2-40)</t>
+    <t>1842: source value from AR CCPC STATEMENTS - PARAGRAPH CODES (349.2-40)</t>
   </si>
   <si>
     <t>Invoice.note</t>
@@ -2720,7 +2726,7 @@
         <v>89</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>90</v>
@@ -2747,7 +2753,7 @@
         <v>79</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="T12" t="s" s="2">
         <v>79</v>
@@ -2762,13 +2768,13 @@
         <v>79</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>79</v>
@@ -2801,19 +2807,19 @@
         <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>79</v>
@@ -2821,10 +2827,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2847,16 +2853,16 @@
         <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2906,7 +2912,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2941,14 +2947,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2967,13 +2973,13 @@
         <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3024,7 +3030,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3045,28 +3051,28 @@
         <v>79</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3085,17 +3091,17 @@
         <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>79</v>
@@ -3144,7 +3150,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3165,24 +3171,24 @@
         <v>79</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3205,13 +3211,13 @@
         <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3262,7 +3268,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3277,30 +3283,30 @@
         <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3323,16 +3329,16 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3382,7 +3388,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3403,13 +3409,13 @@
         <v>79</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>79</v>
@@ -3417,10 +3423,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3443,13 +3449,13 @@
         <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3500,7 +3506,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3521,10 +3527,10 @@
         <v>79</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>79</v>
@@ -3535,10 +3541,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3561,13 +3567,13 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3618,7 +3624,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3642,7 +3648,7 @@
         <v>79</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -3653,10 +3659,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3685,7 +3691,7 @@
         <v>136</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>138</v>
@@ -3738,7 +3744,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3762,7 +3768,7 @@
         <v>79</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>79</v>
@@ -3773,14 +3779,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3802,10 +3808,10 @@
         <v>135</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>138</v>
@@ -3860,7 +3866,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3895,10 +3901,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3921,13 +3927,13 @@
         <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3978,7 +3984,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3999,10 +4005,10 @@
         <v>79</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>79</v>
@@ -4013,10 +4019,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4039,13 +4045,13 @@
         <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4096,7 +4102,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>89</v>
@@ -4117,13 +4123,13 @@
         <v>79</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>79</v>
@@ -4131,10 +4137,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4157,16 +4163,16 @@
         <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4216,7 +4222,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4240,7 +4246,7 @@
         <v>132</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4251,10 +4257,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4277,16 +4283,16 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4336,7 +4342,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4371,10 +4377,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4397,13 +4403,13 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4454,7 +4460,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4475,10 +4481,10 @@
         <v>79</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4489,10 +4495,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4515,13 +4521,13 @@
         <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4572,7 +4578,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4596,7 +4602,7 @@
         <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>79</v>
@@ -4607,10 +4613,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4639,7 +4645,7 @@
         <v>136</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>138</v>
@@ -4692,7 +4698,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4716,7 +4722,7 @@
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -4727,14 +4733,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4756,10 +4762,10 @@
         <v>135</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>138</v>
@@ -4814,7 +4820,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4849,10 +4855,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4875,13 +4881,13 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4932,7 +4938,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4967,10 +4973,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4993,13 +4999,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5038,17 +5044,17 @@
         <v>79</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>89</v>
@@ -5069,10 +5075,10 @@
         <v>79</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5083,13 +5089,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>79</v>
@@ -5111,13 +5117,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5168,7 +5174,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>89</v>
@@ -5183,16 +5189,16 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5203,10 +5209,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5229,13 +5235,13 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5286,7 +5292,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5307,10 +5313,10 @@
         <v>79</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -5321,10 +5327,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5347,13 +5353,13 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5404,7 +5410,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5428,7 +5434,7 @@
         <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -5439,10 +5445,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5471,7 +5477,7 @@
         <v>136</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>138</v>
@@ -5524,7 +5530,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5548,7 +5554,7 @@
         <v>79</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>79</v>
@@ -5559,14 +5565,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5588,10 +5594,10 @@
         <v>135</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>138</v>
@@ -5646,7 +5652,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5681,10 +5687,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5710,10 +5716,10 @@
         <v>109</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5740,13 +5746,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -5764,7 +5770,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>89</v>
@@ -5785,24 +5791,24 @@
         <v>79</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5825,13 +5831,13 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5882,7 +5888,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5903,24 +5909,24 @@
         <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5943,16 +5949,16 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6002,7 +6008,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6023,7 +6029,7 @@
         <v>79</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>79</v>
@@ -6037,10 +6043,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6063,16 +6069,16 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6122,7 +6128,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6137,13 +6143,13 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6157,10 +6163,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6183,13 +6189,13 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6240,7 +6246,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6261,10 +6267,10 @@
         <v>79</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -6275,10 +6281,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6301,13 +6307,13 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6358,7 +6364,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6382,7 +6388,7 @@
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -6393,10 +6399,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6425,7 +6431,7 @@
         <v>136</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>138</v>
@@ -6478,7 +6484,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6502,7 +6508,7 @@
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -6513,14 +6519,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6542,10 +6548,10 @@
         <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>138</v>
@@ -6600,7 +6606,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6635,10 +6641,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6664,10 +6670,10 @@
         <v>109</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6694,13 +6700,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -6718,7 +6724,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>89</v>
@@ -6739,24 +6745,24 @@
         <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6779,13 +6785,13 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6836,7 +6842,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6857,24 +6863,24 @@
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6897,16 +6903,16 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6956,7 +6962,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6977,7 +6983,7 @@
         <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>79</v>
@@ -6991,10 +6997,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7017,16 +7023,16 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7076,7 +7082,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7091,13 +7097,13 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>79</v>
@@ -7111,10 +7117,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7137,16 +7143,16 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7196,7 +7202,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7211,13 +7217,13 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>79</v>
@@ -7231,10 +7237,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7257,16 +7263,16 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7316,7 +7322,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7337,7 +7343,7 @@
         <v>79</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>79</v>
@@ -7351,10 +7357,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7377,16 +7383,16 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7436,7 +7442,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7451,7 +7457,7 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>79</v>
@@ -7471,10 +7477,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7497,13 +7503,13 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7554,7 +7560,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7569,22 +7575,22 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$93</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3554" uniqueCount="413">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -873,10 +873,16 @@
     <t>This code identifies the type of the component.</t>
   </si>
   <si>
+    <t>base</t>
+  </si>
+  <si>
     <t>Codes indicating the kind of the price component.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/invoice-priceComponentType|4.0.1</t>
+  </si>
+  <si>
+    <t>1840-1: fixed value = #base</t>
   </si>
   <si>
     <t>Invoice.lineItem.priceComponent.code</t>
@@ -932,25 +938,295 @@
     <t>The total amount for the Invoice may be calculated as the sum of the line items with surcharges/deductions that apply in certain conditions.  The priceComponent element can be used to offer transparency to the recipient of the Invoice of how the total price was calculated.</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal</t>
+  </si>
+  <si>
+    <t>va-prev-bal</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal.id</t>
+  </si>
+  <si>
     <t>Invoice.totalPriceComponent.id</t>
   </si>
   <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal.extension</t>
+  </si>
+  <si>
     <t>Invoice.totalPriceComponent.extension</t>
   </si>
   <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal.modifierExtension</t>
+  </si>
+  <si>
     <t>Invoice.totalPriceComponent.modifierExtension</t>
   </si>
   <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal.type</t>
+  </si>
+  <si>
     <t>Invoice.totalPriceComponent.type</t>
   </si>
   <si>
+    <t>1829-1: fixed value = #base</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal.code</t>
+  </si>
+  <si>
     <t>Invoice.totalPriceComponent.code</t>
   </si>
   <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal.code.id</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent.code.id</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal.code.extension</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent.code.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal.code.coding</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal.code.text</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>Prev Bal</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>1829-2: fixed value = Prev Bal</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal.factor</t>
+  </si>
+  <si>
     <t>Invoice.totalPriceComponent.factor</t>
   </si>
   <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal.amount</t>
+  </si>
+  <si>
     <t>Invoice.totalPriceComponent.amount</t>
+  </si>
+  <si>
+    <t>1829: source value from AR CCPC STATEMENTS - PREV BAL (349.2-.05)</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-charges</t>
+  </si>
+  <si>
+    <t>va-total-charges</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-charges.id</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-charges.extension</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-charges.modifierExtension</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-charges.type</t>
+  </si>
+  <si>
+    <t>1830-1: fixed value = #base</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-charges.code</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-charges.code.id</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-charges.code.extension</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-charges.code.coding</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-charges.code.text</t>
+  </si>
+  <si>
+    <t>Total Charges</t>
+  </si>
+  <si>
+    <t>1830-2: fixed value = Total Charges</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-charges.factor</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-charges.amount</t>
+  </si>
+  <si>
+    <t>1830: source value from AR CCPC STATEMENTS - TOTAL CHARGES (349.2-.06)</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-credits</t>
+  </si>
+  <si>
+    <t>va-total-credits</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-credits.id</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-credits.extension</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-credits.modifierExtension</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-credits.type</t>
+  </si>
+  <si>
+    <t>1831-1: fixed value = #base</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-credits.code</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-credits.code.id</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-credits.code.extension</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-credits.code.coding</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-credits.code.text</t>
+  </si>
+  <si>
+    <t>Total Credits</t>
+  </si>
+  <si>
+    <t>1831-2: fixed value = Total Credits</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-credits.factor</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-total-credits.amount</t>
+  </si>
+  <si>
+    <t>1831: source value from AR CCPC STATEMENTS - TOTAL CREDITS (349.2-.07)</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-new-balance</t>
+  </si>
+  <si>
+    <t>va-new-balance</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-new-balance.id</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-new-balance.extension</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-new-balance.modifierExtension</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-new-balance.type</t>
+  </si>
+  <si>
+    <t>1832-1: fixed value = #base</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-new-balance.code</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-new-balance.code.id</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-new-balance.code.extension</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-new-balance.code.coding</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-new-balance.code.text</t>
+  </si>
+  <si>
+    <t>New Balance</t>
+  </si>
+  <si>
+    <t>1832-2: fixed value = New Balance</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-new-balance.factor</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-new-balance.amount</t>
   </si>
   <si>
     <t>1832: source value from AR CCPC STATEMENTS - NEW BALANCE (349.2-.08)</t>
@@ -1335,10 +1611,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP52"/>
+  <dimension ref="A1:AP93"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.7578125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="60.35546875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="48.65234375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.91015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -1366,7 +1642,7 @@
     <col min="26" max="26" width="58.40234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="39.109375" customWidth="true" bestFit="true" hidden="true"/>
@@ -1375,7 +1651,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="108.78125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="131.55859375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="31.109375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="45.6171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="97.8125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="29.69921875" customWidth="true" bestFit="true"/>
@@ -5704,7 +5980,7 @@
         <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>79</v>
@@ -5731,7 +6007,7 @@
         <v>79</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>79</v>
+        <v>274</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>79</v>
@@ -5749,10 +6025,10 @@
         <v>158</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -5785,7 +6061,7 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>79</v>
+        <v>277</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>79</v>
@@ -5805,10 +6081,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5834,10 +6110,10 @@
         <v>172</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5888,7 +6164,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5923,10 +6199,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5949,16 +6225,16 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6008,7 +6284,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6029,7 +6305,7 @@
         <v>79</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>79</v>
@@ -6043,10 +6319,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6069,16 +6345,16 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6128,7 +6404,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6143,13 +6419,13 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6163,10 +6439,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6189,13 +6465,13 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6234,19 +6510,17 @@
         <v>79</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>79</v>
+        <v>260</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6281,12 +6555,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>79</v>
       </c>
@@ -6307,13 +6583,13 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>166</v>
+        <v>206</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>212</v>
+        <v>293</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>213</v>
+        <v>294</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6364,19 +6640,19 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>214</v>
+        <v>292</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
@@ -6385,10 +6661,10 @@
         <v>79</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -6399,21 +6675,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>79</v>
@@ -6425,17 +6701,15 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>136</v>
+        <v>212</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -6484,19 +6758,19 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>79</v>
@@ -6519,14 +6793,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>220</v>
+        <v>134</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6539,26 +6813,24 @@
         <v>79</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>221</v>
+        <v>136</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="O44" t="s" s="2">
-        <v>144</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
       </c>
@@ -6606,7 +6878,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6630,7 +6902,7 @@
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>132</v>
+        <v>215</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -6641,42 +6913,46 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>272</v>
+        <v>221</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>79</v>
       </c>
@@ -6700,13 +6976,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>274</v>
+        <v>79</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>275</v>
+        <v>79</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -6724,19 +7000,19 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>271</v>
+        <v>223</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>79</v>
@@ -6745,24 +7021,24 @@
         <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>175</v>
+        <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>178</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6770,13 +7046,13 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>79</v>
@@ -6785,13 +7061,13 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6803,7 +7079,7 @@
         <v>79</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>79</v>
+        <v>274</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>79</v>
@@ -6818,13 +7094,13 @@
         <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>79</v>
+        <v>276</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
@@ -6842,10 +7118,10 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>89</v>
@@ -6857,7 +7133,7 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>79</v>
@@ -6877,10 +7153,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6903,17 +7179,15 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="L47" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>283</v>
-      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -6962,7 +7236,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6983,24 +7257,24 @@
         <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>284</v>
+        <v>175</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>79</v>
+        <v>178</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7014,7 +7288,7 @@
         <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>79</v>
@@ -7023,17 +7297,15 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>286</v>
+        <v>166</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>287</v>
+        <v>212</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7082,7 +7354,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>285</v>
+        <v>214</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7094,19 +7366,19 @@
         <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>300</v>
+        <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>284</v>
+        <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>79</v>
+        <v>215</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7117,42 +7389,42 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>286</v>
+        <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>302</v>
+        <v>136</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>303</v>
+        <v>217</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>283</v>
+        <v>138</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7190,43 +7462,43 @@
         <v>79</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>79</v>
+        <v>313</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>79</v>
+        <v>314</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>79</v>
+        <v>260</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>301</v>
+        <v>218</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>304</v>
+        <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>284</v>
+        <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>79</v>
+        <v>215</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7237,10 +7509,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7251,7 +7523,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -7263,18 +7535,20 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
       </c>
@@ -7322,13 +7596,13 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
@@ -7343,10 +7617,10 @@
         <v>79</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>284</v>
+        <v>323</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>79</v>
+        <v>324</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7357,10 +7631,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7380,21 +7654,23 @@
         <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>309</v>
+        <v>166</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
       </c>
@@ -7403,7 +7679,7 @@
         <v>79</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>79</v>
+        <v>331</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>79</v>
@@ -7442,7 +7718,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7457,16 +7733,16 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>79</v>
+        <v>334</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>79</v>
+        <v>335</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -7477,10 +7753,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7491,10 +7767,10 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>79</v>
@@ -7503,15 +7779,17 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>315</v>
+        <v>282</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>316</v>
+        <v>283</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -7560,13 +7838,13 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>314</v>
+        <v>281</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
@@ -7575,26 +7853,4938 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP52" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="D54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM52" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AO52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP52" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>321</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="D66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="D78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP79" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP80" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP81" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP82" t="s" s="2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP83" t="s" s="2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP84" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP85" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="P86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP86" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="P87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP87" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP89" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP90" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>412</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP52">
+  <autoFilter ref="A1:AP93">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7604,7 +12794,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI51">
+  <conditionalFormatting sqref="A2:AI92">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1325,10 +1325,10 @@
     <t>Invoice.totalPriceComponent:va-marsh-fee.code.text</t>
   </si>
   <si>
-    <t>Marshall Fee</t>
-  </si>
-  <si>
-    <t>1867-2: fixed value = Marshall Fee</t>
+    <t>Marshal Fee</t>
+  </si>
+  <si>
+    <t>1867-2: fixed value = Marshal Fee</t>
   </si>
   <si>
     <t>Invoice.totalPriceComponent:va-marsh-fee.factor</t>
@@ -1337,7 +1337,7 @@
     <t>Invoice.totalPriceComponent:va-marsh-fee.amount</t>
   </si>
   <si>
-    <t>1867: source value from ACCOUNTS RECEIVABLE - MARSHALL FEE (430-74)</t>
+    <t>1867: source value from ACCOUNTS RECEIVABLE - MARSHAL FEE (430-74)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.MarshalFee</t>
@@ -1595,10 +1595,10 @@
     <t>Invoice.totalPriceComponent:va-marsh-fee-paid.code.text</t>
   </si>
   <si>
-    <t>Marshall Fee Paid</t>
-  </si>
-  <si>
-    <t>1872-2: fixed value = Marshall Fee Paid</t>
+    <t>Marshal Fee Paid</t>
+  </si>
+  <si>
+    <t>1872-2: fixed value = Marshal Fee Paid</t>
   </si>
   <si>
     <t>Invoice.totalPriceComponent:va-marsh-fee-paid.factor</t>
@@ -1607,7 +1607,7 @@
     <t>Invoice.totalPriceComponent:va-marsh-fee-paid.amount</t>
   </si>
   <si>
-    <t>1872: source value from ACCOUNTS RECEIVABLE - TOTAL PAID MARSHALL FEE (430-79.1)</t>
+    <t>1872: source value from ACCOUNTS RECEIVABLE - TOTAL PAID MARSHAL FEE (430-79.1)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.TotalMarshalFeePaid</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file AR CCPC STATEMENTS (349.2) to Invoice</t>
+    <t>This StructureDefinition contains the maps for VistA file ACCOUNTS RECEIVABLE (430) to Invoice</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -942,52 +942,55 @@
 </t>
   </si>
   <si>
-    <t>Invoice.totalPriceComponent:va-prev-bal</t>
-  </si>
-  <si>
-    <t>va-prev-bal</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-prev-bal.id</t>
+    <t>Invoice.totalPriceComponent:va-marsh-fee-paid</t>
+  </si>
+  <si>
+    <t>va-marsh-fee-paid</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.id</t>
   </si>
   <si>
     <t>Invoice.totalPriceComponent.id</t>
   </si>
   <si>
-    <t>Invoice.totalPriceComponent:va-prev-bal.extension</t>
+    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.extension</t>
   </si>
   <si>
     <t>Invoice.totalPriceComponent.extension</t>
   </si>
   <si>
-    <t>Invoice.totalPriceComponent:va-prev-bal.modifierExtension</t>
+    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.modifierExtension</t>
   </si>
   <si>
     <t>Invoice.totalPriceComponent.modifierExtension</t>
   </si>
   <si>
-    <t>Invoice.totalPriceComponent:va-prev-bal.type</t>
+    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.type</t>
   </si>
   <si>
     <t>Invoice.totalPriceComponent.type</t>
   </si>
   <si>
-    <t>1829-1: fixed value = #base</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-prev-bal.code</t>
+    <t>surcharge</t>
+  </si>
+  <si>
+    <t>1872-1: fixed value = #surcharge</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.code</t>
   </si>
   <si>
     <t>Invoice.totalPriceComponent.code</t>
   </si>
   <si>
-    <t>Invoice.totalPriceComponent:va-prev-bal.code.id</t>
+    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.code.id</t>
   </si>
   <si>
     <t>Invoice.totalPriceComponent.code.id</t>
   </si>
   <si>
-    <t>Invoice.totalPriceComponent:va-prev-bal.code.extension</t>
+    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.code.extension</t>
   </si>
   <si>
     <t>Invoice.totalPriceComponent.code.extension</t>
@@ -1000,7 +1003,7 @@
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
-    <t>Invoice.totalPriceComponent:va-prev-bal.code.coding</t>
+    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.code.coding</t>
   </si>
   <si>
     <t>Invoice.totalPriceComponent.code.coding</t>
@@ -1031,51 +1034,159 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
+    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.code.text</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>Marshal Fee Paid</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>1872-2: fixed value = Marshal Fee Paid</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.factor</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent.factor</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.amount</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent.amount</t>
+  </si>
+  <si>
+    <t>1872: source value from ACCOUNTS RECEIVABLE - TOTAL PAID MARSHAL FEE (430-79.1)</t>
+  </si>
+  <si>
+    <t>IB.AccountsReceivable.TotalMarshalFeePaid</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-marsh-fee</t>
+  </si>
+  <si>
+    <t>va-marsh-fee</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-marsh-fee.id</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-marsh-fee.extension</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-marsh-fee.modifierExtension</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-marsh-fee.type</t>
+  </si>
+  <si>
+    <t>1867-1: fixed value = #surcharge</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-marsh-fee.code</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-marsh-fee.code.id</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-marsh-fee.code.extension</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-marsh-fee.code.coding</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-marsh-fee.code.text</t>
+  </si>
+  <si>
+    <t>Marshal Fee</t>
+  </si>
+  <si>
+    <t>1867-2: fixed value = Marshal Fee</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-marsh-fee.factor</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-marsh-fee.amount</t>
+  </si>
+  <si>
+    <t>1867: source value from ACCOUNTS RECEIVABLE - MARSHAL FEE (430-74)</t>
+  </si>
+  <si>
+    <t>IB.AccountsReceivable.MarshalFee</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal</t>
+  </si>
+  <si>
+    <t>va-prev-bal</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal.id</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal.extension</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal.modifierExtension</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal.type</t>
+  </si>
+  <si>
+    <t>1829-1: fixed value = #base</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal.code</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal.code.id</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal.code.extension</t>
+  </si>
+  <si>
+    <t>Invoice.totalPriceComponent:va-prev-bal.code.coding</t>
+  </si>
+  <si>
     <t>Invoice.totalPriceComponent:va-prev-bal.code.text</t>
   </si>
   <si>
-    <t>Invoice.totalPriceComponent.code.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
     <t>Prev Bal</t>
   </si>
   <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
     <t>1829-2: fixed value = Prev Bal</t>
   </si>
   <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
     <t>Invoice.totalPriceComponent:va-prev-bal.factor</t>
   </si>
   <si>
-    <t>Invoice.totalPriceComponent.factor</t>
-  </si>
-  <si>
     <t>Invoice.totalPriceComponent:va-prev-bal.amount</t>
   </si>
   <si>
-    <t>Invoice.totalPriceComponent.amount</t>
-  </si>
-  <si>
     <t>1829: source value from AR CCPC STATEMENTS - PREV BAL (349.2-.05)</t>
   </si>
   <si>
@@ -1250,9 +1361,6 @@
     <t>Invoice.totalPriceComponent:va-admin-cost-bal.type</t>
   </si>
   <si>
-    <t>surcharge</t>
-  </si>
-  <si>
     <t>1866-1: fixed value = #surcharge</t>
   </si>
   <si>
@@ -1289,60 +1397,6 @@
     <t>IB.AccountsReceivable.AdministrativeCostBalance</t>
   </si>
   <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee</t>
-  </si>
-  <si>
-    <t>va-marsh-fee</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee.id</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee.extension</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee.modifierExtension</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee.type</t>
-  </si>
-  <si>
-    <t>1867-1: fixed value = #surcharge</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee.code</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee.code.id</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee.code.extension</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee.code.coding</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee.code.text</t>
-  </si>
-  <si>
-    <t>Marshal Fee</t>
-  </si>
-  <si>
-    <t>1867-2: fixed value = Marshal Fee</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee.factor</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee.amount</t>
-  </si>
-  <si>
-    <t>1867: source value from ACCOUNTS RECEIVABLE - MARSHAL FEE (430-74)</t>
-  </si>
-  <si>
-    <t>IB.AccountsReceivable.MarshalFee</t>
-  </si>
-  <si>
     <t>Invoice.totalPriceComponent:va-court-cost</t>
   </si>
   <si>
@@ -1557,60 +1611,6 @@
   </si>
   <si>
     <t>IB.AccountsReceivable.TotalAdministrativeCostPaid</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee-paid</t>
-  </si>
-  <si>
-    <t>va-marsh-fee-paid</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.id</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.extension</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.modifierExtension</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.type</t>
-  </si>
-  <si>
-    <t>1872-1: fixed value = #surcharge</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.code</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.code.id</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.code.extension</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.code.coding</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.code.text</t>
-  </si>
-  <si>
-    <t>Marshal Fee Paid</t>
-  </si>
-  <si>
-    <t>1872-2: fixed value = Marshal Fee Paid</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.factor</t>
-  </si>
-  <si>
-    <t>Invoice.totalPriceComponent:va-marsh-fee-paid.amount</t>
-  </si>
-  <si>
-    <t>1872: source value from ACCOUNTS RECEIVABLE - TOTAL PAID MARSHAL FEE (430-79.1)</t>
-  </si>
-  <si>
-    <t>IB.AccountsReceivable.TotalMarshalFeePaid</t>
   </si>
   <si>
     <t>Invoice.totalPriceComponent:va-court-cost-paid</t>
@@ -7514,7 +7514,7 @@
         <v>79</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>274</v>
+        <v>306</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>79</v>
@@ -7568,7 +7568,7 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>79</v>
@@ -7588,10 +7588,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7706,10 +7706,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7824,10 +7824,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7897,10 +7897,10 @@
         <v>79</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>79</v>
@@ -7944,10 +7944,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7970,19 +7970,19 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -8031,7 +8031,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8052,10 +8052,10 @@
         <v>79</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -8066,10 +8066,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8095,16 +8095,16 @@
         <v>166</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -8114,7 +8114,7 @@
         <v>79</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>79</v>
@@ -8153,7 +8153,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8168,16 +8168,16 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -8188,10 +8188,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8308,10 +8308,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8408,10 +8408,10 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>79</v>
+        <v>342</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>286</v>
@@ -8428,13 +8428,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>292</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>79</v>
@@ -8548,7 +8548,7 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>299</v>
@@ -8666,7 +8666,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>301</v>
@@ -8786,7 +8786,7 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>303</v>
@@ -8908,7 +8908,7 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>305</v>
@@ -8952,7 +8952,7 @@
         <v>79</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>274</v>
+        <v>306</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>79</v>
@@ -9006,7 +9006,7 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>79</v>
@@ -9026,10 +9026,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9144,10 +9144,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9262,10 +9262,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9335,10 +9335,10 @@
         <v>79</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>79</v>
@@ -9382,10 +9382,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9408,19 +9408,19 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
@@ -9469,7 +9469,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9490,10 +9490,10 @@
         <v>79</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9504,10 +9504,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9533,16 +9533,16 @@
         <v>166</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -9552,7 +9552,7 @@
         <v>79</v>
       </c>
       <c r="S63" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="T63" t="s" s="2">
         <v>79</v>
@@ -9591,7 +9591,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9606,16 +9606,16 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9746,10 +9746,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9846,10 +9846,10 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>286</v>
@@ -9866,13 +9866,13 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>292</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>79</v>
@@ -9986,7 +9986,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>299</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>301</v>
@@ -10224,7 +10224,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>303</v>
@@ -10346,7 +10346,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>305</v>
@@ -10444,7 +10444,7 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>79</v>
@@ -10464,10 +10464,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10582,10 +10582,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10700,10 +10700,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10773,10 +10773,10 @@
         <v>79</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>79</v>
@@ -10820,10 +10820,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10846,19 +10846,19 @@
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -10907,7 +10907,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10928,10 +10928,10 @@
         <v>79</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>79</v>
@@ -10942,10 +10942,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10971,16 +10971,16 @@
         <v>166</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -10990,7 +10990,7 @@
         <v>79</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>79</v>
@@ -11029,7 +11029,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11044,16 +11044,16 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>79</v>
@@ -11064,10 +11064,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11184,10 +11184,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11284,7 +11284,7 @@
         <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>79</v>
@@ -11304,13 +11304,13 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>292</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>79</v>
@@ -11424,7 +11424,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>299</v>
@@ -11542,7 +11542,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>301</v>
@@ -11662,7 +11662,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>303</v>
@@ -11784,7 +11784,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>305</v>
@@ -11882,7 +11882,7 @@
         <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>79</v>
@@ -11902,10 +11902,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12020,10 +12020,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12138,10 +12138,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12211,10 +12211,10 @@
         <v>79</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>79</v>
@@ -12258,10 +12258,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12284,19 +12284,19 @@
         <v>90</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>79</v>
@@ -12345,7 +12345,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12366,10 +12366,10 @@
         <v>79</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>79</v>
@@ -12380,10 +12380,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12409,16 +12409,16 @@
         <v>166</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>79</v>
@@ -12428,7 +12428,7 @@
         <v>79</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>79</v>
@@ -12467,7 +12467,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12482,16 +12482,16 @@
         <v>101</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>79</v>
@@ -12502,10 +12502,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12622,10 +12622,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12722,7 +12722,7 @@
         <v>101</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>79</v>
@@ -12742,13 +12742,13 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>292</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>79</v>
@@ -12862,7 +12862,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>299</v>
@@ -12980,7 +12980,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>301</v>
@@ -13100,7 +13100,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>303</v>
@@ -13222,7 +13222,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>305</v>
@@ -13266,7 +13266,7 @@
         <v>79</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>398</v>
+        <v>274</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>79</v>
@@ -13320,7 +13320,7 @@
         <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>79</v>
@@ -13340,10 +13340,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13458,10 +13458,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13576,10 +13576,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13649,10 +13649,10 @@
         <v>79</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>79</v>
@@ -13696,10 +13696,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13722,19 +13722,19 @@
         <v>90</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>79</v>
@@ -13783,7 +13783,7 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13804,10 +13804,10 @@
         <v>79</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>79</v>
@@ -13818,10 +13818,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13847,16 +13847,16 @@
         <v>166</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>79</v>
@@ -13866,7 +13866,7 @@
         <v>79</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>79</v>
@@ -13905,7 +13905,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13920,16 +13920,16 @@
         <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>79</v>
@@ -13940,10 +13940,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14060,10 +14060,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14160,10 +14160,10 @@
         <v>101</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>410</v>
+        <v>79</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>286</v>
@@ -14180,13 +14180,13 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>292</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>79</v>
@@ -14300,7 +14300,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>299</v>
@@ -14418,7 +14418,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>301</v>
@@ -14538,7 +14538,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>303</v>
@@ -14660,7 +14660,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>305</v>
@@ -14704,7 +14704,7 @@
         <v>79</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>398</v>
+        <v>274</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>79</v>
@@ -14758,7 +14758,7 @@
         <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>79</v>
@@ -14778,10 +14778,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14896,10 +14896,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15014,10 +15014,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15087,10 +15087,10 @@
         <v>79</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>79</v>
@@ -15134,10 +15134,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15160,19 +15160,19 @@
         <v>90</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>79</v>
@@ -15221,7 +15221,7 @@
         <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15242,10 +15242,10 @@
         <v>79</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>79</v>
@@ -15256,10 +15256,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15285,16 +15285,16 @@
         <v>166</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>79</v>
@@ -15304,7 +15304,7 @@
         <v>79</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>79</v>
@@ -15343,7 +15343,7 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15358,16 +15358,16 @@
         <v>101</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>79</v>
@@ -15378,10 +15378,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15498,10 +15498,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15598,10 +15598,10 @@
         <v>101</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>428</v>
+        <v>79</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>286</v>
@@ -16142,7 +16142,7 @@
         <v>79</v>
       </c>
       <c r="S118" t="s" s="2">
-        <v>398</v>
+        <v>306</v>
       </c>
       <c r="T118" t="s" s="2">
         <v>79</v>
@@ -16219,7 +16219,7 @@
         <v>436</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16337,7 +16337,7 @@
         <v>437</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16455,7 +16455,7 @@
         <v>438</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16525,10 +16525,10 @@
         <v>79</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>79</v>
@@ -16575,7 +16575,7 @@
         <v>439</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16598,19 +16598,19 @@
         <v>90</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>79</v>
@@ -16659,7 +16659,7 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -16680,10 +16680,10 @@
         <v>79</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>79</v>
@@ -16697,7 +16697,7 @@
         <v>440</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16723,16 +16723,16 @@
         <v>166</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>79</v>
@@ -16781,7 +16781,7 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16802,10 +16802,10 @@
         <v>79</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>79</v>
@@ -16819,7 +16819,7 @@
         <v>443</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16939,7 +16939,7 @@
         <v>444</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17580,7 +17580,7 @@
         <v>79</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>274</v>
+        <v>306</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>79</v>
@@ -17657,7 +17657,7 @@
         <v>454</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17775,7 +17775,7 @@
         <v>455</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17893,7 +17893,7 @@
         <v>456</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17963,10 +17963,10 @@
         <v>79</v>
       </c>
       <c r="AB133" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AC133" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AD133" t="s" s="2">
         <v>79</v>
@@ -18013,7 +18013,7 @@
         <v>457</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18036,19 +18036,19 @@
         <v>90</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>79</v>
@@ -18097,7 +18097,7 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18118,10 +18118,10 @@
         <v>79</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>79</v>
@@ -18135,7 +18135,7 @@
         <v>458</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18161,16 +18161,16 @@
         <v>166</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>79</v>
@@ -18219,7 +18219,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18240,10 +18240,10 @@
         <v>79</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>79</v>
@@ -18257,7 +18257,7 @@
         <v>461</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18377,7 +18377,7 @@
         <v>462</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19018,7 +19018,7 @@
         <v>79</v>
       </c>
       <c r="S142" t="s" s="2">
-        <v>398</v>
+        <v>274</v>
       </c>
       <c r="T142" t="s" s="2">
         <v>79</v>
@@ -19095,7 +19095,7 @@
         <v>472</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19213,7 +19213,7 @@
         <v>473</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19331,7 +19331,7 @@
         <v>474</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19401,10 +19401,10 @@
         <v>79</v>
       </c>
       <c r="AB145" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AC145" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AD145" t="s" s="2">
         <v>79</v>
@@ -19451,7 +19451,7 @@
         <v>475</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19474,19 +19474,19 @@
         <v>90</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>79</v>
@@ -19535,7 +19535,7 @@
         <v>79</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -19556,10 +19556,10 @@
         <v>79</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>79</v>
@@ -19573,7 +19573,7 @@
         <v>476</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19599,16 +19599,16 @@
         <v>166</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>79</v>
@@ -19657,7 +19657,7 @@
         <v>79</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -19678,10 +19678,10 @@
         <v>79</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>79</v>
@@ -19695,7 +19695,7 @@
         <v>479</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19815,7 +19815,7 @@
         <v>480</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20456,7 +20456,7 @@
         <v>79</v>
       </c>
       <c r="S154" t="s" s="2">
-        <v>398</v>
+        <v>306</v>
       </c>
       <c r="T154" t="s" s="2">
         <v>79</v>
@@ -20533,7 +20533,7 @@
         <v>490</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20651,7 +20651,7 @@
         <v>491</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20769,7 +20769,7 @@
         <v>492</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20839,10 +20839,10 @@
         <v>79</v>
       </c>
       <c r="AB157" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AC157" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AD157" t="s" s="2">
         <v>79</v>
@@ -20889,7 +20889,7 @@
         <v>493</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20912,19 +20912,19 @@
         <v>90</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>79</v>
@@ -20973,7 +20973,7 @@
         <v>79</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -20994,10 +20994,10 @@
         <v>79</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>79</v>
@@ -21011,7 +21011,7 @@
         <v>494</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21037,16 +21037,16 @@
         <v>166</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>79</v>
@@ -21095,7 +21095,7 @@
         <v>79</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21116,10 +21116,10 @@
         <v>79</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>79</v>
@@ -21133,7 +21133,7 @@
         <v>497</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21253,7 +21253,7 @@
         <v>498</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21894,7 +21894,7 @@
         <v>79</v>
       </c>
       <c r="S166" t="s" s="2">
-        <v>398</v>
+        <v>306</v>
       </c>
       <c r="T166" t="s" s="2">
         <v>79</v>
@@ -21971,7 +21971,7 @@
         <v>508</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22089,7 +22089,7 @@
         <v>509</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22207,7 +22207,7 @@
         <v>510</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22277,10 +22277,10 @@
         <v>79</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AD169" t="s" s="2">
         <v>79</v>
@@ -22327,7 +22327,7 @@
         <v>511</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22350,19 +22350,19 @@
         <v>90</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>79</v>
@@ -22411,7 +22411,7 @@
         <v>79</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22432,10 +22432,10 @@
         <v>79</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>79</v>
@@ -22449,7 +22449,7 @@
         <v>512</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22475,16 +22475,16 @@
         <v>166</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>79</v>
@@ -22533,7 +22533,7 @@
         <v>79</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -22554,10 +22554,10 @@
         <v>79</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>79</v>
@@ -22571,7 +22571,7 @@
         <v>515</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22691,7 +22691,7 @@
         <v>516</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23332,7 +23332,7 @@
         <v>79</v>
       </c>
       <c r="S178" t="s" s="2">
-        <v>398</v>
+        <v>306</v>
       </c>
       <c r="T178" t="s" s="2">
         <v>79</v>
@@ -23409,7 +23409,7 @@
         <v>526</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23527,7 +23527,7 @@
         <v>527</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23645,7 +23645,7 @@
         <v>528</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -23715,10 +23715,10 @@
         <v>79</v>
       </c>
       <c r="AB181" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AC181" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AD181" t="s" s="2">
         <v>79</v>
@@ -23765,7 +23765,7 @@
         <v>529</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23788,19 +23788,19 @@
         <v>90</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>79</v>
@@ -23849,7 +23849,7 @@
         <v>79</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -23870,10 +23870,10 @@
         <v>79</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>79</v>
@@ -23887,7 +23887,7 @@
         <v>530</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23913,16 +23913,16 @@
         <v>166</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>79</v>
@@ -23971,7 +23971,7 @@
         <v>79</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -23992,10 +23992,10 @@
         <v>79</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>79</v>
@@ -24009,7 +24009,7 @@
         <v>533</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24129,7 +24129,7 @@
         <v>534</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -487,7 +487,7 @@
     <t>Allows Identification of this Invoice instance.</t>
   </si>
   <si>
-    <t>1975: source value from ACCOUNTS RECEIVABLE - BILL NO. (430-.01)</t>
+    <t>1975: source value based on ACCOUNTS RECEIVABLE - BILL NO. (430-.01)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.BillNumber,IB.AccountsReceivableTCSP.BillNumber</t>
@@ -598,7 +598,7 @@
     <t>Links the event to the Patient context.</t>
   </si>
   <si>
-    <t>1976: reference from ACCOUNTS RECEIVABLE - PATIENT &gt; PATIENT (430-7 &gt; 2-)</t>
+    <t>1976: reference based on ACCOUNTS RECEIVABLE - PATIENT &gt; PATIENT (430-7 &gt; 2-)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.PatientIEN,IB.AccountsReceivableComment.PatientIEN,IB.AccountsReceivableDescription.PatientIEN,IB.AccountsReceivableFiscalYear.PatientIEN,IB.AccountsReceivableRepayDate.PatientIEN,IB.AccountsReceivableTCSP.PatientIEN,IB.AccountsReceivableTCSP.PatientSID</t>
@@ -630,10 +630,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-dpi-17-1818:430-9 &gt; 340-.01: if patient then Patient {null}</t>
-  </si>
-  <si>
-    <t>1818: reference from ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - DEBTOR (430-9 &gt; 340-.01) case patient</t>
+dpi-17-1818:If patient then reference Patient based on (430-9 &gt; 340-.01) {null}</t>
+  </si>
+  <si>
+    <t>1818: reference based on ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - DEBTOR (430-9 &gt; 340-.01) if patient</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.ARDebtorIEN
@@ -665,7 +665,7 @@
     <t>The list of types may be constrained as appropriate for the type of charge item.</t>
   </si>
   <si>
-    <t>1977: source value from ACCOUNTS RECEIVABLE - DATE BILL PREPARED (430-10)</t>
+    <t>1977: source value based on ACCOUNTS RECEIVABLE - DATE BILL PREPARED (430-10)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.BillPreparedDateTime,IB.AccountsReceivableComment.BillPreparedDateTime,IB.AccountsReceivableDescription.BillPreparedDateTime,IB.AccountsReceivableFiscalYear.BillPreparedDateTime,IB.AccountsReceivableRepayDate.BillPreparedDateTime,IB.AccountsReceivableTCSP.BillPreparedDateTime</t>
@@ -784,7 +784,7 @@
     <t>Practitioners and Devices can be associated with multiple organizations. It has to be made clear, on behalf of which Organization the services have been rendered.</t>
   </si>
   <si>
-    <t>2007: source value from ACCOUNTS RECEIVABLE - SITE (430-12)</t>
+    <t>2007: source value based on ACCOUNTS RECEIVABLE - SITE (430-12)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.InstitutionIEN</t>
@@ -1085,7 +1085,7 @@
     <t>Invoice.lineItem:va-charges.priceComponent.amount</t>
   </si>
   <si>
-    <t>1840: source value from INTEGRATED BILLING ACTION - TOTAL CHARGE (350-.07)</t>
+    <t>1840: source value based on INTEGRATED BILLING ACTION - TOTAL CHARGE (350-.07)</t>
   </si>
   <si>
     <t>IB.IBAction.TotalCharge</t>
@@ -1197,7 +1197,7 @@
     <t>Invoice.lineItem:va-interest.priceComponent:va-marshal-fee-charged.amount</t>
   </si>
   <si>
-    <t>1999: source value from AR TRANSACTION - MARSHAL FEE (433-25)</t>
+    <t>1999: source value based on AR TRANSACTION - MARSHAL FEE (433-25)</t>
   </si>
   <si>
     <t>IB.ARTransaction.MarshalFee</t>
@@ -1251,7 +1251,7 @@
     <t>Invoice.lineItem:va-interest.priceComponent:va-court-cost-charged.amount</t>
   </si>
   <si>
-    <t>2000: source value from AR TRANSACTION - COURT COST (433-26)</t>
+    <t>2000: source value based on AR TRANSACTION - COURT COST (433-26)</t>
   </si>
   <si>
     <t>IB.ARTransaction.CourtCost</t>
@@ -1305,7 +1305,7 @@
     <t>Invoice.lineItem:va-interest.priceComponent:va-interest-charged.amount</t>
   </si>
   <si>
-    <t>2001: source value from AR TRANSACTION - INT.CHARGE (433-27)</t>
+    <t>2001: source value based on AR TRANSACTION - INT.CHARGE (433-27)</t>
   </si>
   <si>
     <t>IB.ARTransaction.InterestCharge</t>
@@ -1359,7 +1359,7 @@
     <t>Invoice.lineItem:va-interest.priceComponent:va-admin-charged.amount</t>
   </si>
   <si>
-    <t>2002: source value from AR TRANSACTION - ADM.CHARGE (433-28)</t>
+    <t>2002: source value based on AR TRANSACTION - ADM.CHARGE (433-28)</t>
   </si>
   <si>
     <t>IB.ARTransaction.AdministrativeCharge</t>
@@ -1458,7 +1458,7 @@
     <t>Invoice.totalPriceComponent.amount</t>
   </si>
   <si>
-    <t>1828: source value from ACCOUNTS RECEIVABLE - ORIGINAL AMOUNT (430-3)</t>
+    <t>1828: source value based on ACCOUNTS RECEIVABLE - ORIGINAL AMOUNT (430-3)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.OriginalBillAmount</t>
@@ -1512,7 +1512,7 @@
     <t>Invoice.totalPriceComponent:va-curr-bal.amount</t>
   </si>
   <si>
-    <t>1829: source value from ACCOUNTS RECEIVABLE - CURRENT BALANCE (430-11)</t>
+    <t>1829: source value based on ACCOUNTS RECEIVABLE - CURRENT BALANCE (430-11)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.CurrentBalance</t>
@@ -1566,7 +1566,7 @@
     <t>Invoice.totalPriceComponent:va-amend-amt.amount</t>
   </si>
   <si>
-    <t>1830: source value from ACCOUNTS RECEIVABLE - AMENDED AMOUNT (430-35)</t>
+    <t>1830: source value based on ACCOUNTS RECEIVABLE - AMENDED AMOUNT (430-35)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.BillAmendAmount</t>
@@ -1620,7 +1620,7 @@
     <t>Invoice.totalPriceComponent:va-principal-bal.amount</t>
   </si>
   <si>
-    <t>1831: source value from ACCOUNTS RECEIVABLE - PRINCIPAL BALANCE (430-71)</t>
+    <t>1831: source value based on ACCOUNTS RECEIVABLE - PRINCIPAL BALANCE (430-71)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.PrincipalBalance</t>
@@ -1674,7 +1674,7 @@
     <t>Invoice.totalPriceComponent:va-interest-bal.amount</t>
   </si>
   <si>
-    <t>1832: source value from ACCOUNTS RECEIVABLE - INTEREST BALANCE (430-72)</t>
+    <t>1832: source value based on ACCOUNTS RECEIVABLE - INTEREST BALANCE (430-72)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.InterestBalance</t>
@@ -1728,7 +1728,7 @@
     <t>Invoice.totalPriceComponent:va-admin-cost-bal.amount</t>
   </si>
   <si>
-    <t>1866: source value from ACCOUNTS RECEIVABLE - ADMINISTRATIVE COST BALANCE (430-73)</t>
+    <t>1866: source value based on ACCOUNTS RECEIVABLE - ADMINISTRATIVE COST BALANCE (430-73)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.AdministrativeCostBalance</t>
@@ -1782,7 +1782,7 @@
     <t>Invoice.totalPriceComponent:va-marsh-fee.amount</t>
   </si>
   <si>
-    <t>1867: source value from ACCOUNTS RECEIVABLE - MARSHAL FEE (430-74)</t>
+    <t>1867: source value based on ACCOUNTS RECEIVABLE - MARSHAL FEE (430-74)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.MarshalFee</t>
@@ -1836,7 +1836,7 @@
     <t>Invoice.totalPriceComponent:va-court-cost.amount</t>
   </si>
   <si>
-    <t>1868: source value from ACCOUNTS RECEIVABLE - COURT COST (430-75)</t>
+    <t>1868: source value based on ACCOUNTS RECEIVABLE - COURT COST (430-75)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.CourtCost</t>
@@ -1890,7 +1890,7 @@
     <t>Invoice.totalPriceComponent:va-principal-paid.amount</t>
   </si>
   <si>
-    <t>1869: source value from ACCOUNTS RECEIVABLE - TOTAL PAID PRINCIPAL (430-77)</t>
+    <t>1869: source value based on ACCOUNTS RECEIVABLE - TOTAL PAID PRINCIPAL (430-77)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.TotalPrincipalPaid</t>
@@ -1944,7 +1944,7 @@
     <t>Invoice.totalPriceComponent:va-interest-paid.amount</t>
   </si>
   <si>
-    <t>1870: source value from ACCOUNTS RECEIVABLE - TOTAL PAID INTEREST (430-78)</t>
+    <t>1870: source value based on ACCOUNTS RECEIVABLE - TOTAL PAID INTEREST (430-78)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.TotalInterestPaid</t>
@@ -1998,7 +1998,7 @@
     <t>Invoice.totalPriceComponent:va-admin-cost-paid.amount</t>
   </si>
   <si>
-    <t>1871: source value from ACCOUNTS RECEIVABLE - TOTAL PAID ADMINISTRATIVE COST (430-79)</t>
+    <t>1871: source value based on ACCOUNTS RECEIVABLE - TOTAL PAID ADMINISTRATIVE COST (430-79)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.TotalAdministrativeCostPaid</t>
@@ -2052,7 +2052,7 @@
     <t>Invoice.totalPriceComponent:va-marsh-fee-paid.amount</t>
   </si>
   <si>
-    <t>1872: source value from ACCOUNTS RECEIVABLE - TOTAL PAID MARSHAL FEE (430-79.1)</t>
+    <t>1872: source value based on ACCOUNTS RECEIVABLE - TOTAL PAID MARSHAL FEE (430-79.1)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.TotalMarshalFeePaid</t>
@@ -2106,7 +2106,7 @@
     <t>Invoice.totalPriceComponent:va-court-cost-paid.amount</t>
   </si>
   <si>
-    <t>1873: source value from ACCOUNTS RECEIVABLE - TOTAL PAID COURT COST (430-79.2)</t>
+    <t>1873: source value based on ACCOUNTS RECEIVABLE - TOTAL PAID COURT COST (430-79.2)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.TotalCourtCostPaid</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -633,7 +633,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-dpi-17-1818:If patient then reference Patient based on (430-9 &gt; 340-.01) {null}</t>
+dpi-17-1818:If patient then reference Patient based on (430-9 &gt; 340-.01) {true}</t>
   </si>
   <si>
     <t>1818: reference based on ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - DEBTOR (430-9 &gt; 340-.01) if patient</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -601,7 +601,7 @@
     <t>Links the event to the Patient context.</t>
   </si>
   <si>
-    <t>1976: reference based on ACCOUNTS RECEIVABLE - PATIENT &gt; PATIENT (430-7 &gt; 2-)</t>
+    <t>1976: reference based on ACCOUNTS RECEIVABLE - PATIENT (430-7)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.PatientIEN,IB.AccountsReceivableComment.PatientIEN,IB.AccountsReceivableDescription.PatientIEN,IB.AccountsReceivableFiscalYear.PatientIEN,IB.AccountsReceivableRepayDate.PatientIEN,IB.AccountsReceivableTCSP.PatientIEN,IB.AccountsReceivableTCSP.PatientSID</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10711" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10711" uniqueCount="704">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -968,11 +968,15 @@
     <t>chargeItemReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/DebtPortalChargeItemcharges)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/DebtPortalChargeItemcharges|http://va.gov/fhir/StructureDefinition/DebtPortalChargeItemremoved)
 </t>
   </si>
   <si>
-    <t>1834: reference</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+dpi-17-1834:If INTEGRATED BILLING ACTION - PARENT CHARGE = INTEGRATED BILLING ACTION - IEN then reference ChargeItemcharges based on (null) {true}dpi-17-2220:If INTEGRATED BILLING ACTION - PARENT CHARGE &lt;&gt; INTEGRATED BILLING ACTION - IEN then reference ChargeItemremoved based on (null) {true}</t>
+  </si>
+  <si>
+    <t>2220: reference if INTEGRATED BILLING ACTION - PARENT CHARGE &lt;&gt; INTEGRATED BILLING ACTION - IEN</t>
   </si>
   <si>
     <t>Invoice.lineItem:va-charges.priceComponent</t>
@@ -2498,7 +2502,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="77.93359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="137.28125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -8004,10 +8008,10 @@
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>305</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>79</v>
@@ -8027,7 +8031,7 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>270</v>
@@ -8145,7 +8149,7 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>273</v>
@@ -8263,7 +8267,7 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>274</v>
@@ -8383,7 +8387,7 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>275</v>
@@ -8505,7 +8509,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>276</v>
@@ -8549,7 +8553,7 @@
         <v>79</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>79</v>
@@ -8603,7 +8607,7 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>79</v>
@@ -8623,7 +8627,7 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>281</v>
@@ -8741,10 +8745,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8859,10 +8863,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8932,10 +8936,10 @@
         <v>79</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>79</v>
@@ -8979,10 +8983,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9005,19 +9009,19 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -9066,7 +9070,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9087,10 +9091,10 @@
         <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -9101,10 +9105,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9130,16 +9134,16 @@
         <v>168</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -9149,7 +9153,7 @@
         <v>79</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>79</v>
@@ -9188,7 +9192,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9203,16 +9207,16 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -9223,7 +9227,7 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>284</v>
@@ -9343,7 +9347,7 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>290</v>
@@ -9443,10 +9447,10 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>289</v>
@@ -9463,13 +9467,13 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>254</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>79</v>
@@ -9583,7 +9587,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>259</v>
@@ -9701,7 +9705,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>260</v>
@@ -9821,7 +9825,7 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>261</v>
@@ -9943,7 +9947,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>262</v>
@@ -10061,7 +10065,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>266</v>
@@ -10177,7 +10181,7 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>266</v>
@@ -10205,7 +10209,7 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>268</v>
@@ -10277,7 +10281,7 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>79</v>
@@ -10297,7 +10301,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>270</v>
@@ -10413,7 +10417,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>273</v>
@@ -10531,7 +10535,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>274</v>
@@ -10651,7 +10655,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>275</v>
@@ -10773,7 +10777,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>276</v>
@@ -10891,7 +10895,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>281</v>
@@ -11009,7 +11013,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>284</v>
@@ -11129,7 +11133,7 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>290</v>
@@ -11249,13 +11253,13 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>270</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>79</v>
@@ -11369,7 +11373,7 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>273</v>
@@ -11487,7 +11491,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>274</v>
@@ -11607,7 +11611,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>275</v>
@@ -11729,7 +11733,7 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>276</v>
@@ -11773,7 +11777,7 @@
         <v>79</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>79</v>
@@ -11827,7 +11831,7 @@
         <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>79</v>
@@ -11847,7 +11851,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>281</v>
@@ -11965,10 +11969,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12083,10 +12087,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12156,10 +12160,10 @@
         <v>79</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>79</v>
@@ -12203,10 +12207,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12229,19 +12233,19 @@
         <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>79</v>
@@ -12290,7 +12294,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12311,10 +12315,10 @@
         <v>79</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>79</v>
@@ -12325,10 +12329,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12354,16 +12358,16 @@
         <v>168</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>79</v>
@@ -12373,7 +12377,7 @@
         <v>79</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>79</v>
@@ -12412,7 +12416,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12427,16 +12431,16 @@
         <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>79</v>
@@ -12447,7 +12451,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>284</v>
@@ -12567,7 +12571,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>290</v>
@@ -12667,10 +12671,10 @@
         <v>101</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>289</v>
@@ -12687,13 +12691,13 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>270</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>79</v>
@@ -12807,7 +12811,7 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>273</v>
@@ -12925,7 +12929,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>274</v>
@@ -13045,7 +13049,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>275</v>
@@ -13167,7 +13171,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>276</v>
@@ -13211,7 +13215,7 @@
         <v>79</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>79</v>
@@ -13265,7 +13269,7 @@
         <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>79</v>
@@ -13285,7 +13289,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>281</v>
@@ -13403,10 +13407,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13521,10 +13525,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13594,10 +13598,10 @@
         <v>79</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>79</v>
@@ -13641,10 +13645,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13667,19 +13671,19 @@
         <v>90</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>79</v>
@@ -13728,7 +13732,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13749,10 +13753,10 @@
         <v>79</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>79</v>
@@ -13763,10 +13767,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13792,16 +13796,16 @@
         <v>168</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>79</v>
@@ -13811,7 +13815,7 @@
         <v>79</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>79</v>
@@ -13850,7 +13854,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13865,16 +13869,16 @@
         <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>79</v>
@@ -13885,7 +13889,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>284</v>
@@ -14005,7 +14009,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>290</v>
@@ -14105,10 +14109,10 @@
         <v>101</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>289</v>
@@ -14125,13 +14129,13 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>270</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>79</v>
@@ -14245,7 +14249,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>273</v>
@@ -14363,7 +14367,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>274</v>
@@ -14483,7 +14487,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>275</v>
@@ -14605,7 +14609,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>276</v>
@@ -14649,7 +14653,7 @@
         <v>79</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>79</v>
@@ -14703,7 +14707,7 @@
         <v>101</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>79</v>
@@ -14723,7 +14727,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>281</v>
@@ -14841,10 +14845,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14959,10 +14963,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15032,10 +15036,10 @@
         <v>79</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>79</v>
@@ -15079,10 +15083,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15105,19 +15109,19 @@
         <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>79</v>
@@ -15166,7 +15170,7 @@
         <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15187,10 +15191,10 @@
         <v>79</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>79</v>
@@ -15201,10 +15205,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15230,16 +15234,16 @@
         <v>168</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>79</v>
@@ -15249,7 +15253,7 @@
         <v>79</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>79</v>
@@ -15288,7 +15292,7 @@
         <v>79</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15303,16 +15307,16 @@
         <v>101</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>79</v>
@@ -15323,7 +15327,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>284</v>
@@ -15443,7 +15447,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>290</v>
@@ -15543,10 +15547,10 @@
         <v>101</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>289</v>
@@ -15563,13 +15567,13 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>270</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>79</v>
@@ -15683,7 +15687,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>273</v>
@@ -15801,7 +15805,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>274</v>
@@ -15921,7 +15925,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>275</v>
@@ -16043,7 +16047,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>276</v>
@@ -16087,7 +16091,7 @@
         <v>79</v>
       </c>
       <c r="S114" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T114" t="s" s="2">
         <v>79</v>
@@ -16141,7 +16145,7 @@
         <v>101</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>79</v>
@@ -16161,7 +16165,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>281</v>
@@ -16279,10 +16283,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16397,10 +16401,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16470,10 +16474,10 @@
         <v>79</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC117" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD117" t="s" s="2">
         <v>79</v>
@@ -16517,10 +16521,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16543,19 +16547,19 @@
         <v>90</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>79</v>
@@ -16604,7 +16608,7 @@
         <v>79</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16625,10 +16629,10 @@
         <v>79</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>79</v>
@@ -16639,10 +16643,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16668,16 +16672,16 @@
         <v>168</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -16687,7 +16691,7 @@
         <v>79</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>79</v>
@@ -16726,7 +16730,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16741,16 +16745,16 @@
         <v>101</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>79</v>
@@ -16761,7 +16765,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>284</v>
@@ -16881,7 +16885,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>290</v>
@@ -16981,10 +16985,10 @@
         <v>101</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>289</v>
@@ -17001,10 +17005,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17030,10 +17034,10 @@
         <v>82</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17082,7 +17086,7 @@
         <v>258</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17117,13 +17121,13 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>79</v>
@@ -17148,10 +17152,10 @@
         <v>213</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -17202,7 +17206,7 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17237,10 +17241,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17355,10 +17359,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17475,10 +17479,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17597,10 +17601,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17641,7 +17645,7 @@
         <v>79</v>
       </c>
       <c r="S127" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="T127" t="s" s="2">
         <v>79</v>
@@ -17695,7 +17699,7 @@
         <v>101</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>79</v>
@@ -17715,10 +17719,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17833,10 +17837,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17951,10 +17955,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18024,10 +18028,10 @@
         <v>79</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>79</v>
@@ -18071,10 +18075,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18097,19 +18101,19 @@
         <v>90</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>79</v>
@@ -18158,7 +18162,7 @@
         <v>79</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18179,10 +18183,10 @@
         <v>79</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>79</v>
@@ -18193,10 +18197,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18222,16 +18226,16 @@
         <v>168</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>79</v>
@@ -18241,7 +18245,7 @@
         <v>79</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>79</v>
@@ -18280,7 +18284,7 @@
         <v>79</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18295,16 +18299,16 @@
         <v>101</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>79</v>
@@ -18315,10 +18319,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18435,10 +18439,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18535,10 +18539,10 @@
         <v>101</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>289</v>
@@ -18555,13 +18559,13 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>79</v>
@@ -18586,10 +18590,10 @@
         <v>213</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18640,7 +18644,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18675,10 +18679,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18793,10 +18797,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18913,10 +18917,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19035,10 +19039,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19079,7 +19083,7 @@
         <v>79</v>
       </c>
       <c r="S139" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="T139" t="s" s="2">
         <v>79</v>
@@ -19133,7 +19137,7 @@
         <v>101</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>79</v>
@@ -19153,10 +19157,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19271,10 +19275,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19389,10 +19393,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19462,10 +19466,10 @@
         <v>79</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>79</v>
@@ -19509,10 +19513,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19535,19 +19539,19 @@
         <v>90</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>79</v>
@@ -19596,7 +19600,7 @@
         <v>79</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19617,10 +19621,10 @@
         <v>79</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>79</v>
@@ -19631,10 +19635,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19660,16 +19664,16 @@
         <v>168</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>79</v>
@@ -19679,7 +19683,7 @@
         <v>79</v>
       </c>
       <c r="S144" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>79</v>
@@ -19718,7 +19722,7 @@
         <v>79</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -19733,16 +19737,16 @@
         <v>101</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AL144" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>79</v>
@@ -19753,10 +19757,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19873,10 +19877,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19973,10 +19977,10 @@
         <v>101</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AM146" t="s" s="2">
         <v>289</v>
@@ -19993,13 +19997,13 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D147" t="s" s="2">
         <v>79</v>
@@ -20024,10 +20028,10 @@
         <v>213</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -20078,7 +20082,7 @@
         <v>79</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20113,10 +20117,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20231,10 +20235,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20351,10 +20355,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20473,10 +20477,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20517,7 +20521,7 @@
         <v>79</v>
       </c>
       <c r="S151" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="T151" t="s" s="2">
         <v>79</v>
@@ -20571,7 +20575,7 @@
         <v>101</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>79</v>
@@ -20591,10 +20595,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20709,10 +20713,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20827,10 +20831,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20900,10 +20904,10 @@
         <v>79</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>79</v>
@@ -20947,10 +20951,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20973,19 +20977,19 @@
         <v>90</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>79</v>
@@ -21034,7 +21038,7 @@
         <v>79</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21055,10 +21059,10 @@
         <v>79</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>79</v>
@@ -21069,10 +21073,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21098,16 +21102,16 @@
         <v>168</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>79</v>
@@ -21117,7 +21121,7 @@
         <v>79</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>79</v>
@@ -21156,7 +21160,7 @@
         <v>79</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21171,16 +21175,16 @@
         <v>101</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>79</v>
@@ -21191,10 +21195,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21311,10 +21315,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21411,10 +21415,10 @@
         <v>101</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AM158" t="s" s="2">
         <v>289</v>
@@ -21431,13 +21435,13 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D159" t="s" s="2">
         <v>79</v>
@@ -21462,10 +21466,10 @@
         <v>213</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -21516,7 +21520,7 @@
         <v>79</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21551,10 +21555,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21669,10 +21673,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21789,10 +21793,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21911,10 +21915,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21955,7 +21959,7 @@
         <v>79</v>
       </c>
       <c r="S163" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="T163" t="s" s="2">
         <v>79</v>
@@ -22009,7 +22013,7 @@
         <v>101</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>79</v>
@@ -22029,10 +22033,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22147,10 +22151,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22265,10 +22269,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22338,10 +22342,10 @@
         <v>79</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC166" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD166" t="s" s="2">
         <v>79</v>
@@ -22385,10 +22389,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22411,19 +22415,19 @@
         <v>90</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>79</v>
@@ -22472,7 +22476,7 @@
         <v>79</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22493,10 +22497,10 @@
         <v>79</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>79</v>
@@ -22507,10 +22511,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22536,16 +22540,16 @@
         <v>168</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>79</v>
@@ -22555,7 +22559,7 @@
         <v>79</v>
       </c>
       <c r="S168" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>79</v>
@@ -22594,7 +22598,7 @@
         <v>79</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22609,16 +22613,16 @@
         <v>101</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>79</v>
@@ -22629,10 +22633,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22749,10 +22753,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22849,10 +22853,10 @@
         <v>101</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>289</v>
@@ -22869,13 +22873,13 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D171" t="s" s="2">
         <v>79</v>
@@ -22900,10 +22904,10 @@
         <v>213</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -22954,7 +22958,7 @@
         <v>79</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -22989,10 +22993,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23107,10 +23111,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23227,10 +23231,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23349,10 +23353,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23393,7 +23397,7 @@
         <v>79</v>
       </c>
       <c r="S175" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T175" t="s" s="2">
         <v>79</v>
@@ -23447,7 +23451,7 @@
         <v>101</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AL175" t="s" s="2">
         <v>79</v>
@@ -23467,10 +23471,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23585,10 +23589,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23703,10 +23707,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23776,10 +23780,10 @@
         <v>79</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC178" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD178" t="s" s="2">
         <v>79</v>
@@ -23823,10 +23827,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23849,19 +23853,19 @@
         <v>90</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>79</v>
@@ -23910,7 +23914,7 @@
         <v>79</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -23931,10 +23935,10 @@
         <v>79</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>79</v>
@@ -23945,10 +23949,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23974,16 +23978,16 @@
         <v>168</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>79</v>
@@ -23993,7 +23997,7 @@
         <v>79</v>
       </c>
       <c r="S180" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="T180" t="s" s="2">
         <v>79</v>
@@ -24032,7 +24036,7 @@
         <v>79</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -24047,16 +24051,16 @@
         <v>101</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AL180" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO180" t="s" s="2">
         <v>79</v>
@@ -24067,10 +24071,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24187,10 +24191,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24287,10 +24291,10 @@
         <v>101</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AM182" t="s" s="2">
         <v>289</v>
@@ -24307,13 +24311,13 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D183" t="s" s="2">
         <v>79</v>
@@ -24338,10 +24342,10 @@
         <v>213</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -24392,7 +24396,7 @@
         <v>79</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24427,10 +24431,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24545,10 +24549,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24665,10 +24669,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24787,10 +24791,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24831,7 +24835,7 @@
         <v>79</v>
       </c>
       <c r="S187" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T187" t="s" s="2">
         <v>79</v>
@@ -24885,7 +24889,7 @@
         <v>101</v>
       </c>
       <c r="AK187" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AL187" t="s" s="2">
         <v>79</v>
@@ -24905,10 +24909,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25023,10 +25027,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25141,10 +25145,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25214,10 +25218,10 @@
         <v>79</v>
       </c>
       <c r="AB190" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC190" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD190" t="s" s="2">
         <v>79</v>
@@ -25261,10 +25265,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25287,19 +25291,19 @@
         <v>90</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>79</v>
@@ -25348,7 +25352,7 @@
         <v>79</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>80</v>
@@ -25369,10 +25373,10 @@
         <v>79</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO191" t="s" s="2">
         <v>79</v>
@@ -25383,10 +25387,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25412,16 +25416,16 @@
         <v>168</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>79</v>
@@ -25431,7 +25435,7 @@
         <v>79</v>
       </c>
       <c r="S192" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="T192" t="s" s="2">
         <v>79</v>
@@ -25470,7 +25474,7 @@
         <v>79</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
@@ -25485,16 +25489,16 @@
         <v>101</v>
       </c>
       <c r="AK192" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AL192" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO192" t="s" s="2">
         <v>79</v>
@@ -25505,10 +25509,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25625,10 +25629,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25725,10 +25729,10 @@
         <v>101</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AM194" t="s" s="2">
         <v>289</v>
@@ -25745,13 +25749,13 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D195" t="s" s="2">
         <v>79</v>
@@ -25776,10 +25780,10 @@
         <v>213</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -25830,7 +25834,7 @@
         <v>79</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -25865,10 +25869,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -25983,10 +25987,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26103,10 +26107,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26225,10 +26229,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26269,7 +26273,7 @@
         <v>79</v>
       </c>
       <c r="S199" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T199" t="s" s="2">
         <v>79</v>
@@ -26323,7 +26327,7 @@
         <v>101</v>
       </c>
       <c r="AK199" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AL199" t="s" s="2">
         <v>79</v>
@@ -26343,10 +26347,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26461,10 +26465,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26579,10 +26583,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -26652,10 +26656,10 @@
         <v>79</v>
       </c>
       <c r="AB202" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC202" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD202" t="s" s="2">
         <v>79</v>
@@ -26699,10 +26703,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -26725,19 +26729,19 @@
         <v>90</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O203" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>79</v>
@@ -26786,7 +26790,7 @@
         <v>79</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>80</v>
@@ -26807,10 +26811,10 @@
         <v>79</v>
       </c>
       <c r="AM203" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN203" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO203" t="s" s="2">
         <v>79</v>
@@ -26821,10 +26825,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -26850,16 +26854,16 @@
         <v>168</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O204" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>79</v>
@@ -26869,7 +26873,7 @@
         <v>79</v>
       </c>
       <c r="S204" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="T204" t="s" s="2">
         <v>79</v>
@@ -26908,7 +26912,7 @@
         <v>79</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>80</v>
@@ -26923,16 +26927,16 @@
         <v>101</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AL204" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM204" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN204" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO204" t="s" s="2">
         <v>79</v>
@@ -26943,10 +26947,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27063,10 +27067,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27163,10 +27167,10 @@
         <v>101</v>
       </c>
       <c r="AK206" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AL206" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AM206" t="s" s="2">
         <v>289</v>
@@ -27183,13 +27187,13 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D207" t="s" s="2">
         <v>79</v>
@@ -27214,10 +27218,10 @@
         <v>213</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
@@ -27268,7 +27272,7 @@
         <v>79</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>80</v>
@@ -27303,10 +27307,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27421,10 +27425,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27541,10 +27545,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27663,10 +27667,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -27707,7 +27711,7 @@
         <v>79</v>
       </c>
       <c r="S211" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T211" t="s" s="2">
         <v>79</v>
@@ -27761,7 +27765,7 @@
         <v>101</v>
       </c>
       <c r="AK211" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AL211" t="s" s="2">
         <v>79</v>
@@ -27781,10 +27785,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -27899,10 +27903,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28017,10 +28021,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28090,10 +28094,10 @@
         <v>79</v>
       </c>
       <c r="AB214" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC214" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD214" t="s" s="2">
         <v>79</v>
@@ -28137,10 +28141,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28163,19 +28167,19 @@
         <v>90</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N215" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O215" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>79</v>
@@ -28224,7 +28228,7 @@
         <v>79</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>80</v>
@@ -28245,10 +28249,10 @@
         <v>79</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>79</v>
@@ -28259,10 +28263,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28288,16 +28292,16 @@
         <v>168</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O216" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>79</v>
@@ -28307,7 +28311,7 @@
         <v>79</v>
       </c>
       <c r="S216" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="T216" t="s" s="2">
         <v>79</v>
@@ -28346,7 +28350,7 @@
         <v>79</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>80</v>
@@ -28361,16 +28365,16 @@
         <v>101</v>
       </c>
       <c r="AK216" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AL216" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>79</v>
@@ -28381,10 +28385,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28501,10 +28505,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -28601,10 +28605,10 @@
         <v>101</v>
       </c>
       <c r="AK218" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AL218" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AM218" t="s" s="2">
         <v>289</v>
@@ -28621,13 +28625,13 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D219" t="s" s="2">
         <v>79</v>
@@ -28652,10 +28656,10 @@
         <v>213</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N219" s="2"/>
       <c r="O219" s="2"/>
@@ -28706,7 +28710,7 @@
         <v>79</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>80</v>
@@ -28741,10 +28745,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -28859,10 +28863,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -28979,10 +28983,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29101,10 +29105,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29145,7 +29149,7 @@
         <v>79</v>
       </c>
       <c r="S223" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="T223" t="s" s="2">
         <v>79</v>
@@ -29199,7 +29203,7 @@
         <v>101</v>
       </c>
       <c r="AK223" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AL223" t="s" s="2">
         <v>79</v>
@@ -29219,10 +29223,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29337,10 +29341,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29455,10 +29459,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -29528,10 +29532,10 @@
         <v>79</v>
       </c>
       <c r="AB226" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC226" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD226" t="s" s="2">
         <v>79</v>
@@ -29575,10 +29579,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -29601,19 +29605,19 @@
         <v>90</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N227" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O227" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P227" t="s" s="2">
         <v>79</v>
@@ -29662,7 +29666,7 @@
         <v>79</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>80</v>
@@ -29683,10 +29687,10 @@
         <v>79</v>
       </c>
       <c r="AM227" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN227" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO227" t="s" s="2">
         <v>79</v>
@@ -29697,10 +29701,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -29726,16 +29730,16 @@
         <v>168</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O228" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P228" t="s" s="2">
         <v>79</v>
@@ -29745,7 +29749,7 @@
         <v>79</v>
       </c>
       <c r="S228" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="T228" t="s" s="2">
         <v>79</v>
@@ -29784,7 +29788,7 @@
         <v>79</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>80</v>
@@ -29799,16 +29803,16 @@
         <v>101</v>
       </c>
       <c r="AK228" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AL228" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM228" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN228" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO228" t="s" s="2">
         <v>79</v>
@@ -29819,10 +29823,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -29939,10 +29943,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30039,10 +30043,10 @@
         <v>101</v>
       </c>
       <c r="AK230" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AL230" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AM230" t="s" s="2">
         <v>289</v>
@@ -30059,13 +30063,13 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D231" t="s" s="2">
         <v>79</v>
@@ -30090,10 +30094,10 @@
         <v>213</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" s="2"/>
@@ -30144,7 +30148,7 @@
         <v>79</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>80</v>
@@ -30179,10 +30183,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -30297,10 +30301,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30417,10 +30421,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30539,10 +30543,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30583,7 +30587,7 @@
         <v>79</v>
       </c>
       <c r="S235" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T235" t="s" s="2">
         <v>79</v>
@@ -30637,7 +30641,7 @@
         <v>101</v>
       </c>
       <c r="AK235" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AL235" t="s" s="2">
         <v>79</v>
@@ -30657,10 +30661,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -30775,10 +30779,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -30893,10 +30897,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -30966,10 +30970,10 @@
         <v>79</v>
       </c>
       <c r="AB238" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC238" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD238" t="s" s="2">
         <v>79</v>
@@ -31013,10 +31017,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -31039,19 +31043,19 @@
         <v>90</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N239" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O239" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P239" t="s" s="2">
         <v>79</v>
@@ -31100,7 +31104,7 @@
         <v>79</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>80</v>
@@ -31121,10 +31125,10 @@
         <v>79</v>
       </c>
       <c r="AM239" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN239" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO239" t="s" s="2">
         <v>79</v>
@@ -31135,10 +31139,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -31164,16 +31168,16 @@
         <v>168</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N240" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O240" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P240" t="s" s="2">
         <v>79</v>
@@ -31183,7 +31187,7 @@
         <v>79</v>
       </c>
       <c r="S240" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="T240" t="s" s="2">
         <v>79</v>
@@ -31222,7 +31226,7 @@
         <v>79</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>80</v>
@@ -31237,16 +31241,16 @@
         <v>101</v>
       </c>
       <c r="AK240" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AL240" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM240" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN240" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO240" t="s" s="2">
         <v>79</v>
@@ -31257,10 +31261,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -31377,10 +31381,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -31477,10 +31481,10 @@
         <v>101</v>
       </c>
       <c r="AK242" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AL242" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AM242" t="s" s="2">
         <v>289</v>
@@ -31497,13 +31501,13 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D243" t="s" s="2">
         <v>79</v>
@@ -31528,10 +31532,10 @@
         <v>213</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N243" s="2"/>
       <c r="O243" s="2"/>
@@ -31582,7 +31586,7 @@
         <v>79</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>80</v>
@@ -31617,10 +31621,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -31735,10 +31739,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -31855,10 +31859,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -31977,10 +31981,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -32021,7 +32025,7 @@
         <v>79</v>
       </c>
       <c r="S247" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T247" t="s" s="2">
         <v>79</v>
@@ -32075,7 +32079,7 @@
         <v>101</v>
       </c>
       <c r="AK247" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AL247" t="s" s="2">
         <v>79</v>
@@ -32095,10 +32099,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -32213,10 +32217,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -32331,10 +32335,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -32404,10 +32408,10 @@
         <v>79</v>
       </c>
       <c r="AB250" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC250" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD250" t="s" s="2">
         <v>79</v>
@@ -32451,10 +32455,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32477,19 +32481,19 @@
         <v>90</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N251" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O251" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P251" t="s" s="2">
         <v>79</v>
@@ -32538,7 +32542,7 @@
         <v>79</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>80</v>
@@ -32559,10 +32563,10 @@
         <v>79</v>
       </c>
       <c r="AM251" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN251" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO251" t="s" s="2">
         <v>79</v>
@@ -32573,10 +32577,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -32602,16 +32606,16 @@
         <v>168</v>
       </c>
       <c r="L252" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M252" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N252" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O252" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P252" t="s" s="2">
         <v>79</v>
@@ -32621,7 +32625,7 @@
         <v>79</v>
       </c>
       <c r="S252" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="T252" t="s" s="2">
         <v>79</v>
@@ -32660,7 +32664,7 @@
         <v>79</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>80</v>
@@ -32675,16 +32679,16 @@
         <v>101</v>
       </c>
       <c r="AK252" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AL252" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM252" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN252" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO252" t="s" s="2">
         <v>79</v>
@@ -32695,10 +32699,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -32815,10 +32819,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -32915,10 +32919,10 @@
         <v>101</v>
       </c>
       <c r="AK254" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AL254" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AM254" t="s" s="2">
         <v>289</v>
@@ -32935,13 +32939,13 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D255" t="s" s="2">
         <v>79</v>
@@ -32966,10 +32970,10 @@
         <v>213</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N255" s="2"/>
       <c r="O255" s="2"/>
@@ -33020,7 +33024,7 @@
         <v>79</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>80</v>
@@ -33055,10 +33059,10 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -33173,10 +33177,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -33293,10 +33297,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -33415,10 +33419,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -33459,7 +33463,7 @@
         <v>79</v>
       </c>
       <c r="S259" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T259" t="s" s="2">
         <v>79</v>
@@ -33513,7 +33517,7 @@
         <v>101</v>
       </c>
       <c r="AK259" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AL259" t="s" s="2">
         <v>79</v>
@@ -33533,10 +33537,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -33651,10 +33655,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33769,10 +33773,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -33842,10 +33846,10 @@
         <v>79</v>
       </c>
       <c r="AB262" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC262" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD262" t="s" s="2">
         <v>79</v>
@@ -33889,10 +33893,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -33915,19 +33919,19 @@
         <v>90</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N263" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O263" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P263" t="s" s="2">
         <v>79</v>
@@ -33976,7 +33980,7 @@
         <v>79</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>80</v>
@@ -33997,10 +34001,10 @@
         <v>79</v>
       </c>
       <c r="AM263" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN263" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO263" t="s" s="2">
         <v>79</v>
@@ -34011,10 +34015,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -34040,16 +34044,16 @@
         <v>168</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N264" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O264" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P264" t="s" s="2">
         <v>79</v>
@@ -34059,7 +34063,7 @@
         <v>79</v>
       </c>
       <c r="S264" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="T264" t="s" s="2">
         <v>79</v>
@@ -34098,7 +34102,7 @@
         <v>79</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>80</v>
@@ -34113,16 +34117,16 @@
         <v>101</v>
       </c>
       <c r="AK264" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AL264" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM264" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN264" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO264" t="s" s="2">
         <v>79</v>
@@ -34133,10 +34137,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -34253,10 +34257,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -34353,10 +34357,10 @@
         <v>101</v>
       </c>
       <c r="AK266" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AL266" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AM266" t="s" s="2">
         <v>289</v>
@@ -34373,13 +34377,13 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D267" t="s" s="2">
         <v>79</v>
@@ -34404,10 +34408,10 @@
         <v>213</v>
       </c>
       <c r="L267" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M267" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N267" s="2"/>
       <c r="O267" s="2"/>
@@ -34458,7 +34462,7 @@
         <v>79</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>80</v>
@@ -34493,10 +34497,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -34611,10 +34615,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -34731,10 +34735,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -34853,10 +34857,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -34897,7 +34901,7 @@
         <v>79</v>
       </c>
       <c r="S271" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T271" t="s" s="2">
         <v>79</v>
@@ -34951,7 +34955,7 @@
         <v>101</v>
       </c>
       <c r="AK271" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AL271" t="s" s="2">
         <v>79</v>
@@ -34971,10 +34975,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -35089,10 +35093,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -35207,10 +35211,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -35280,10 +35284,10 @@
         <v>79</v>
       </c>
       <c r="AB274" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC274" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD274" t="s" s="2">
         <v>79</v>
@@ -35327,10 +35331,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -35353,19 +35357,19 @@
         <v>90</v>
       </c>
       <c r="K275" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L275" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M275" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N275" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O275" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P275" t="s" s="2">
         <v>79</v>
@@ -35414,7 +35418,7 @@
         <v>79</v>
       </c>
       <c r="AF275" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG275" t="s" s="2">
         <v>80</v>
@@ -35435,10 +35439,10 @@
         <v>79</v>
       </c>
       <c r="AM275" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN275" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO275" t="s" s="2">
         <v>79</v>
@@ -35449,10 +35453,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -35478,16 +35482,16 @@
         <v>168</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N276" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O276" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P276" t="s" s="2">
         <v>79</v>
@@ -35497,7 +35501,7 @@
         <v>79</v>
       </c>
       <c r="S276" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="T276" t="s" s="2">
         <v>79</v>
@@ -35536,7 +35540,7 @@
         <v>79</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>80</v>
@@ -35551,16 +35555,16 @@
         <v>101</v>
       </c>
       <c r="AK276" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AL276" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM276" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN276" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO276" t="s" s="2">
         <v>79</v>
@@ -35571,10 +35575,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -35691,10 +35695,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -35791,10 +35795,10 @@
         <v>101</v>
       </c>
       <c r="AK278" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AL278" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AM278" t="s" s="2">
         <v>289</v>
@@ -35811,10 +35815,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -35840,10 +35844,10 @@
         <v>291</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="M279" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="N279" t="s" s="2">
         <v>288</v>
@@ -35896,7 +35900,7 @@
         <v>79</v>
       </c>
       <c r="AF279" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AG279" t="s" s="2">
         <v>80</v>
@@ -35931,10 +35935,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -35960,10 +35964,10 @@
         <v>291</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M280" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N280" t="s" s="2">
         <v>288</v>
@@ -36016,7 +36020,7 @@
         <v>79</v>
       </c>
       <c r="AF280" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG280" t="s" s="2">
         <v>80</v>
@@ -36051,10 +36055,10 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -36077,16 +36081,16 @@
         <v>79</v>
       </c>
       <c r="K281" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N281" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="O281" s="2"/>
       <c r="P281" t="s" s="2">
@@ -36136,7 +36140,7 @@
         <v>79</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>80</v>
@@ -36171,10 +36175,10 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -36197,13 +36201,13 @@
         <v>79</v>
       </c>
       <c r="K282" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="N282" s="2"/>
       <c r="O282" s="2"/>
@@ -36254,7 +36258,7 @@
         <v>79</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>80</v>
@@ -36275,16 +36279,16 @@
         <v>79</v>
       </c>
       <c r="AM282" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AN282" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AO282" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP282" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
